--- a/outputs/Block2_Pipeline_Derived_Summary_v12.xlsx
+++ b/outputs/Block2_Pipeline_Derived_Summary_v12.xlsx
@@ -408,7 +408,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>8.925000000000001</v>
+        <v>14.45</v>
       </c>
       <c r="C2">
         <v>40</v>
